--- a/data/source/xlsx/PartitionMembers.xlsx
+++ b/data/source/xlsx/PartitionMembers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,7 +635,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>campo_de_fiori</t>
+          <t>camera_sicurezza_questura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>campo_marzio</t>
+          <t>campo_de_fiori</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>campo_verano</t>
+          <t>campo_marzio</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -671,19 +671,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cantinone_albano</t>
+          <t>campo_verano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>casa_crocchiapani</t>
+          <t>cantina_zamira</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>casal_bruciato</t>
+          <t>cantinone_albano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>casello_km_20_25</t>
+          <t>casa_crocchiapani</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cassero</t>
+          <t>casal_bruciato</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>castel_di_leva</t>
+          <t>casello_km_20_25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>castel_gandolfo</t>
+          <t>cassero</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>castel_savello</t>
+          <t>castel_di_leva</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -767,7 +767,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>castelli_romani</t>
+          <t>castel_gandolfo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>castello</t>
+          <t>castel_savello</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>casuccia_zamira</t>
+          <t>castelli_romani</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cecchina</t>
+          <t>castello</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -815,43 +815,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>celio</t>
+          <t>casuccia_zamira</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>centrale_del_latte</t>
+          <t>cecchina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ciampino</t>
+          <t>celio</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cobianchi</t>
+          <t>centrale_del_latte</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -863,19 +863,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>collegio_romano</t>
+          <t>ciampino</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>colonnato_san_pietro</t>
+          <t>cobianchi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corso_umberto</t>
+          <t>collegio_romano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cupola_san_pietro</t>
+          <t>colonnato_san_pietro</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dazeglio</t>
+          <t>corso_umberto</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -923,31 +923,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ditta_ciurlani</t>
+          <t>cupola_san_pietro</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>divino_amore</t>
+          <t>dazeglio</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>due_santi</t>
+          <t>ditta_ciurlani</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>edicola_due_santi</t>
+          <t>divino_amore</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -971,19 +971,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>esquilino</t>
+          <t>due_santi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>falcognana</t>
+          <t>edicola_due_santi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -995,31 +995,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fontana_di_papa</t>
+          <t>esquilino</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fontanella_di_borghese</t>
+          <t>falcognana</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>frascati</t>
+          <t>fontana_di_papa</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1031,79 +1031,79 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>frattocchie</t>
+          <t>fontanella_di_borghese</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>gianicolo</t>
+          <t>frascati</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gioielliere_catellani</t>
+          <t>frattocchie</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>grotta_de_sor_pippo</t>
+          <t>gianicolo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>grottaferrata</t>
+          <t>gioielliere_catellani</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>istituto_dellenciclopedia_treccani</t>
+          <t>grotta_de_sor_pippo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>laboratorio_zamira</t>
+          <t>grottaferrata</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>largo_brancaccio</t>
+          <t>istituto_dellenciclopedia_treccani</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1127,19 +1127,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>lungara</t>
+          <t>laboratorio_zamira</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>maccheronaro</t>
+          <t>largo_brancaccio</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1151,43 +1151,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>marino</t>
+          <t>lungara</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>monte_algido</t>
+          <t>maccheronaro</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>monti</t>
+          <t>marino</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>orto_vigna_due_santi</t>
+          <t>monte_algido</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1199,43 +1199,43 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>palazzo</t>
+          <t>monti</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>palazzo_219</t>
+          <t>orto_vigna_due_santi</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>palazzo_chigi</t>
+          <t>palazzo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>palazzo_del_mappamondo</t>
+          <t>palazzo_219</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>palazzo_pio</t>
+          <t>palazzo_chigi</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>palazzo_ruspoli</t>
+          <t>palazzo_del_mappamondo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>palazzo_simonetti</t>
+          <t>palazzo_pio</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>pantheon</t>
+          <t>palazzo_ruspoli</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1295,55 +1295,55 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>passaggio_livello_casal_bruciato</t>
+          <t>palazzo_simonetti</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>pavona</t>
+          <t>pantheon</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>pensione_burgess</t>
+          <t>passaggio_livello_casal_bruciato</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>piani_alti_219</t>
+          <t>pavona</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>piazza_colonna</t>
+          <t>pensione_burgess</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>piazza_di_pietra</t>
+          <t>piani_alti_219</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>piazza_di_spagna</t>
+          <t>piazza_colonna</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>piazza_esedra</t>
+          <t>piazza_di_pietra</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>piazza_montanara</t>
+          <t>piazza_di_spagna</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>piazza_pollarola</t>
+          <t>piazza_esedra</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>piazza_rusticucci</t>
+          <t>piazza_montanara</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>piazza_san_giovanni</t>
+          <t>piazza_pollarola</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>piazza_san_lorenzo_in_lucina</t>
+          <t>piazza_rusticucci</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>piazza_verdi</t>
+          <t>piazza_san_giovanni</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>piazza_vittorio_emanuele</t>
+          <t>piazza_san_lorenzo_in_lucina</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>piccarozzi</t>
+          <t>piazza_verdi</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>pincio</t>
+          <t>piazza_vittorio_emanuele</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>policlinico</t>
+          <t>piccarozzi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -1511,43 +1511,43 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ponte_di_santa_fumia</t>
+          <t>pincio</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ponte_divino_amore</t>
+          <t>policlinico</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>porta_angelica</t>
+          <t>ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>porta_borgo_marino</t>
+          <t>ponte_divino_amore</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>porta_latina</t>
+          <t>porta_angelica</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1571,19 +1571,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>porta_maggiore</t>
+          <t>porta_borgo_marino</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>porta_pinciana</t>
+          <t>porta_latina</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>porta_san_paolo</t>
+          <t>porta_maggiore</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>pozzo_delle_cornacchie</t>
+          <t>porta_pinciana</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -1619,19 +1619,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>pozzofondo</t>
+          <t>porta_san_paolo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>prati</t>
+          <t>pozzo_delle_cornacchie</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>pratica_di_mare</t>
+          <t>pozzofondo</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>publicii_clivio_de</t>
+          <t>prati</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -1667,19 +1667,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>quartierino_prati</t>
+          <t>pratica_di_mare</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>quattro_cantoni</t>
+          <t>publicii_clivio_de</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -1691,7 +1691,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>regina_coeli</t>
+          <t>quartierino_prati</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ripetta</t>
+          <t>quattro_cantoni</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -1715,31 +1715,31 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>robine_vecchie</t>
+          <t>regina_coeli</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>rocca_di_papa</t>
+          <t>ripetta</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>rocca_orsina</t>
+          <t>robine_vecchie</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -1751,31 +1751,31 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>rocca_savella</t>
+          <t>rocca_di_papa</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sacro_cuore</t>
+          <t>rocca_orsina</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>san_camillo</t>
+          <t>rocca_savella</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -1787,19 +1787,19 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>san_carlo_alle_quattro_fontane</t>
+          <t>sacello_responsale</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>san_clemente</t>
+          <t>sacro_cuore</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>san_giovanni</t>
+          <t>san_camillo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>san_giovanni_in_laterano</t>
+          <t>san_carlo_alle_quattro_fontane</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>san_lorenzo_al_verano</t>
+          <t>san_clemente</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>san_luigi_de_francesi</t>
+          <t>san_giovanni</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>san_martino_ai_monti</t>
+          <t>san_giovanni_in_laterano</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -1871,7 +1871,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>san_silvestro_in_capite</t>
+          <t>san_lorenzo_al_verano</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>santa_chiara</t>
+          <t>san_luigi_de_francesi</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>santa_croce_in_gerusalemme</t>
+          <t>san_martino_ai_monti</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>santa_margherita_in_abitacolo</t>
+          <t>san_silvestro_in_capite</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>santa_maria_della_neve</t>
+          <t>santa_chiara</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -1931,7 +1931,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>santa_maria_in_aquiro</t>
+          <t>santa_croce_in_gerusalemme</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -1943,7 +1943,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>santa_maria_in_domnica</t>
+          <t>santa_margherita_in_abitacolo</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>santa_maria_in_porta_paradisi</t>
+          <t>santa_maria_della_neve</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>santa_maria_maggiore</t>
+          <t>santa_maria_in_aquiro</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>santa_maria_sopra_minerva</t>
+          <t>santa_maria_in_domnica</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -1991,19 +1991,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>santa_palomba</t>
+          <t>santa_maria_in_porta_paradisi</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>santa_rita_invitacolo</t>
+          <t>santa_maria_maggiore</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>santagnese_in_agone</t>
+          <t>santa_maria_sopra_minerva</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -2027,19 +2027,19 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>santagostino</t>
+          <t>santa_palomba</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>santandrea_della_valle</t>
+          <t>santa_rita_invitacolo</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -2051,7 +2051,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>santanna</t>
+          <t>santagnese_in_agone</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -2063,7 +2063,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>santantonio_da_padova</t>
+          <t>santagostino</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>santi_quattro_coronati</t>
+          <t>santandrea_della_valle</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>santo_stefano_del_cacco_celio_santo_stefano</t>
+          <t>santanna</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>santo_stefano_rotondo</t>
+          <t>santantonio_da_padova</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>scala_a</t>
+          <t>santi_quattro_coronati</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>scala_b</t>
+          <t>santo_stefano_del_cacco_celio_santo_stefano</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -2135,7 +2135,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>santo_stefano_rotondo</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2147,91 +2147,91 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>solforata</t>
+          <t>scala_a</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>stazione_carabinieri_castello</t>
+          <t>scala_b</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>stazione_pavona</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>suburra</t>
+          <t>solforata</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>teatro_jovinelli</t>
+          <t>stazione_carabinieri_castello</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tempio_di_agrippa</t>
+          <t>stazione_pavona</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tenenza_carabinieri_marino</t>
+          <t>suburra</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>termini</t>
+          <t>teatro_jovinelli</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>terzo_piano_219</t>
+          <t>tempio_di_agrippa</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tivoli</t>
+          <t>tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -2267,31 +2267,31 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>termini</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tor_ser_paolo</t>
+          <t>terzo_piano_219</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>torraccio</t>
+          <t>tivoli</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -2303,43 +2303,43 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>traforo</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>trastevere</t>
+          <t>tor_ser_paolo</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>via_boncompagni</t>
+          <t>torraccio</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>via_botteghe_oscure</t>
+          <t>traforo</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -2351,7 +2351,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>via_campo_marzio</t>
+          <t>trastevere</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>via_capo_dafrica</t>
+          <t>via_boncompagni</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -2375,7 +2375,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>via_carlo_alberto</t>
+          <t>via_botteghe_oscure</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -2387,7 +2387,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>via_colonna_vittoria</t>
+          <t>via_campo_marzio</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>via_dazeglio</t>
+          <t>via_capo_dafrica</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>via_de_merli</t>
+          <t>via_carlo_alberto</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>via_de_querceti</t>
+          <t>via_colonna_vittoria</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>via_degli_zingari</t>
+          <t>via_dazeglio</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -2447,7 +2447,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>via_dei_banchi_vecchi</t>
+          <t>via_de_merli</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>via_dei_capocci</t>
+          <t>via_de_querceti</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>via_dei_fienili</t>
+          <t>via_degli_zingari</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>via_dei_greci</t>
+          <t>via_dei_banchi_vecchi</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -2495,7 +2495,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>via_dei_serpenti</t>
+          <t>via_dei_capocci</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>via_del_corso</t>
+          <t>via_dei_fienili</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>via_del_gesu</t>
+          <t>via_dei_greci</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -2531,19 +2531,19 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>via_del_gobbo</t>
+          <t>via_dei_serpenti</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>via_del_parlamento</t>
+          <t>via_del_corso</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -2555,31 +2555,31 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>via_della_falcognana</t>
+          <t>via_del_gesu</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>via_della_navicella</t>
+          <t>via_del_gobbo</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>via_della_palombella</t>
+          <t>via_del_parlamento</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -2591,19 +2591,19 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>via_della_scrofa</t>
+          <t>via_della_falcognana</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>via_delle_coppelle</t>
+          <t>via_della_navicella</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -2615,7 +2615,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>via_di_ferro</t>
+          <t>via_della_palombella</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -2627,7 +2627,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>via_di_grotta_pinta</t>
+          <t>via_della_scrofa</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>via_di_pietra</t>
+          <t>via_delle_coppelle</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>via_di_san_paolo_della_croce</t>
+          <t>via_di_ferro</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>via_di_santo_stefano_rotondo</t>
+          <t>via_di_grotta_pinta</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>via_frangipane</t>
+          <t>via_di_pietra</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -2687,7 +2687,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>via_labbricana</t>
+          <t>via_di_san_paolo_della_croce</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>via_lanza</t>
+          <t>via_di_santo_stefano_rotondo</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>via_ludovisi</t>
+          <t>via_frangipane</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -2723,7 +2723,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>via_mamiani</t>
+          <t>via_labbricana</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -2735,19 +2735,19 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>via_massimo_dazeglio</t>
+          <t>via_lanza</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>via_merulana</t>
+          <t>via_ludovisi</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>via_milano</t>
+          <t>via_mamiani</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -2771,19 +2771,19 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>via_monte_caprino</t>
+          <t>via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>via_montebello</t>
+          <t>via_merulana</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -2795,7 +2795,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>via_nicotera</t>
+          <t>via_milano</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -2807,7 +2807,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>via_orazio</t>
+          <t>via_monte_caprino</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -2819,7 +2819,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>via_panisperna</t>
+          <t>via_montebello</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>via_popolonia</t>
+          <t>via_nicotera</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -2843,7 +2843,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>via_ricasoli</t>
+          <t>via_orazio</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -2855,7 +2855,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>via_valadier</t>
+          <t>via_panisperna</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>via_veneto</t>
+          <t>via_popolonia</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -2879,7 +2879,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>via_venti_settembre</t>
+          <t>via_ricasoli</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -2891,7 +2891,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>via_villari</t>
+          <t>via_valadier</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -2903,7 +2903,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>via_zanardelli</t>
+          <t>via_veneto</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>viale_della_regina</t>
+          <t>via_venti_settembre</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -2927,7 +2927,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>viale_liegi</t>
+          <t>via_villari</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>viale_regina_margherita</t>
+          <t>via_zanardelli</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -2951,7 +2951,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>vicolo_ciancaleoni</t>
+          <t>viale_della_regina</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>vicolo_della_bucimazza</t>
+          <t>viale_liegi</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>vicolo_delle_grotte_del_teatro</t>
+          <t>viale_regina_margherita</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>villa_borghese</t>
+          <t>vicolo_ciancaleoni</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>villa_celimontana</t>
+          <t>vicolo_della_bucimazza</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -3011,31 +3011,31 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>villa_deste</t>
+          <t>vicolo_delle_grotte_del_teatro</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>villa_gregoriana</t>
+          <t>villa_borghese</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>campagna_romana</t>
+          <t>roma_citta</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>villino_lungotevere</t>
+          <t>villa_celimontana</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -3047,34 +3047,70 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>viminale</t>
+          <t>villa_deste</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>vite</t>
+          <t>villa_gregoriana</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>roma_citta</t>
+          <t>campagna_romana</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
+          <t>villino_lungotevere</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>roma_citta</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>viminale</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>roma_citta</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>vite</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>roma_citta</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
           <t>zagarolo</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>campagna_romana</t>
         </is>
